--- a/outputs/homophobie/homophobie_scenario_julie_run001_results.xlsx
+++ b/outputs/homophobie/homophobie_scenario_julie_run001_results.xlsx
@@ -541,87 +541,87 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>LLM_confidence</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>used_expert_annotations</t>
+          <t>LLM_used_expert_annotations</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>topic</t>
+          <t>LLM_topic</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Colère</t>
+          <t>LLM_Colère</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Dégoût</t>
+          <t>LLM_Dégoût</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Joie</t>
+          <t>LLM_Joie</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Peur</t>
+          <t>LLM_Peur</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Surprise</t>
+          <t>LLM_Surprise</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Tristesse</t>
+          <t>LLM_Tristesse</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Admiration</t>
+          <t>LLM_Admiration</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Culpabilité</t>
+          <t>LLM_Culpabilité</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Embarras</t>
+          <t>LLM_Embarras</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Fierté</t>
+          <t>LLM_Fierté</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Jalousie</t>
+          <t>LLM_Jalousie</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>rationale</t>
+          <t>LLM_rationale</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>ambiguities</t>
+          <t>LLM_ambiguities</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>n_emotions_active</t>
+          <t>LLM_n_emotions_active</t>
         </is>
       </c>
     </row>
